--- a/forms/20260512固定资产申领单-冯雪.xlsx
+++ b/forms/20260512固定资产申领单-冯雪.xlsx
@@ -105,7 +105,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -444,12 +444,6 @@
         <color rgb="FF3D3D3D"/>
       </bottom>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="6">
@@ -564,16 +558,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -594,14 +585,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -609,7 +594,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1062,7 +1056,7 @@
           <t xml:space="preserve"> 使用人</t>
         </is>
       </c>
-      <c r="F2" s="37" t="inlineStr">
+      <c r="F2" s="36" t="inlineStr">
         <is>
           <t>冯雪</t>
         </is>
@@ -1072,168 +1066,168 @@
           <t xml:space="preserve"> 领用/回收时间</t>
         </is>
       </c>
-      <c r="H2" s="38" t="inlineStr">
+      <c r="H2" s="37" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customFormat="1" customHeight="1" s="32">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>领用/回收资产</t>
         </is>
       </c>
-      <c r="B3" s="40" t="n"/>
-      <c r="C3" s="40" t="n"/>
-      <c r="D3" s="40" t="n"/>
-      <c r="E3" s="40" t="n"/>
-      <c r="F3" s="40" t="n"/>
-      <c r="G3" s="40" t="n"/>
-      <c r="H3" s="41" t="n"/>
+      <c r="B3" s="39" t="n"/>
+      <c r="C3" s="39" t="n"/>
+      <c r="D3" s="39" t="n"/>
+      <c r="E3" s="39" t="n"/>
+      <c r="F3" s="39" t="n"/>
+      <c r="G3" s="39" t="n"/>
+      <c r="H3" s="40" t="n"/>
     </row>
     <row r="4" ht="31" customFormat="1" customHeight="1" s="32">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>资产名称</t>
         </is>
       </c>
-      <c r="C4" s="44" t="n"/>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>品牌型号</t>
         </is>
       </c>
-      <c r="E4" s="44" t="n"/>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>安装地点</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>资产编码</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="5" ht="31" customFormat="1" customHeight="1" s="32">
-      <c r="A5" s="46" t="n">
+      <c r="A5" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="47" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>显示器</t>
         </is>
       </c>
-      <c r="C5" s="44" t="n"/>
-      <c r="D5" s="48" t="inlineStr">
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="47" t="inlineStr">
         <is>
           <t>曙光WLCD-24FH20</t>
         </is>
       </c>
-      <c r="E5" s="44" t="n"/>
-      <c r="F5" s="47" t="inlineStr">
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="46" t="inlineStr">
         <is>
           <t>2号楼425</t>
         </is>
       </c>
-      <c r="G5" s="48" t="inlineStr">
+      <c r="G5" s="47" t="inlineStr">
         <is>
           <t>TY2022000016XSQ</t>
         </is>
       </c>
-      <c r="H5" s="49" t="inlineStr">
+      <c r="H5" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">回收 </t>
         </is>
       </c>
     </row>
     <row r="6" ht="31" customFormat="1" customHeight="1" s="32">
-      <c r="A6" s="46" t="n">
+      <c r="A6" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>显示器</t>
         </is>
       </c>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="C6" s="43" t="n"/>
+      <c r="D6" s="47" t="inlineStr">
         <is>
           <t>联合创新29B2F</t>
         </is>
       </c>
-      <c r="E6" s="44" t="n"/>
-      <c r="F6" s="47" t="inlineStr">
+      <c r="E6" s="43" t="n"/>
+      <c r="F6" s="46" t="inlineStr">
         <is>
           <t>2号楼425</t>
         </is>
       </c>
-      <c r="G6" s="48" t="inlineStr">
+      <c r="G6" s="47" t="inlineStr">
         <is>
           <t>510122MB1867896224000062XSQ</t>
         </is>
       </c>
-      <c r="H6" s="49" t="inlineStr">
+      <c r="H6" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">发放 </t>
         </is>
       </c>
     </row>
     <row r="7" ht="31" customFormat="1" customHeight="1" s="32">
-      <c r="A7" s="46" t="n">
+      <c r="A7" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="50" t="n"/>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="50" t="n"/>
-      <c r="E7" s="44" t="n"/>
-      <c r="F7" s="50" t="n"/>
-      <c r="G7" s="50" t="n"/>
-      <c r="H7" s="51" t="n"/>
+      <c r="B7" s="49" t="n"/>
+      <c r="C7" s="43" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="43" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="50" t="n"/>
     </row>
     <row r="8" ht="31" customFormat="1" customHeight="1" s="32">
-      <c r="A8" s="46" t="n">
+      <c r="A8" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="50" t="n"/>
-      <c r="C8" s="44" t="n"/>
-      <c r="D8" s="50" t="n"/>
-      <c r="E8" s="44" t="n"/>
-      <c r="F8" s="50" t="n"/>
-      <c r="G8" s="50" t="n"/>
-      <c r="H8" s="51" t="n"/>
+      <c r="B8" s="49" t="n"/>
+      <c r="C8" s="43" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="43" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="50" t="n"/>
     </row>
     <row r="9" ht="31" customFormat="1" customHeight="1" s="32">
-      <c r="A9" s="46" t="n">
+      <c r="A9" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="50" t="n"/>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="50" t="n"/>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="50" t="n"/>
-      <c r="G9" s="50" t="n"/>
-      <c r="H9" s="51" t="n"/>
+      <c r="B9" s="49" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="49" t="n"/>
+      <c r="E9" s="43" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="50" t="n"/>
     </row>
     <row r="10" ht="54" customFormat="1" customHeight="1" s="32">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>申请事由</t>
         </is>
       </c>
-      <c r="B10" s="52" t="n"/>
-      <c r="C10" s="38" t="inlineStr"/>
+      <c r="B10" s="51" t="n"/>
+      <c r="C10" s="52" t="inlineStr"/>
       <c r="D10" s="53" t="n"/>
       <c r="E10" s="53" t="n"/>
       <c r="F10" s="53" t="n"/>
@@ -1261,7 +1255,7 @@
 审核意见</t>
         </is>
       </c>
-      <c r="B12" s="52" t="n"/>
+      <c r="B12" s="51" t="n"/>
       <c r="C12" s="61" t="n"/>
       <c r="H12" s="62" t="n"/>
     </row>
@@ -1301,7 +1295,7 @@
 审核意见</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n"/>
+      <c r="B15" s="51" t="n"/>
       <c r="C15" s="71" t="inlineStr">
         <is>
           <t>上述（ ）-（ ）项固定资产已于 年 月 日发放/回收到位。</t>
